--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55321-2025 artfynd.xlsx
+++ b/artfynd/A 55321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137092482</v>
       </c>
       <c r="B2" t="n">
-        <v>99469</v>
+        <v>99473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
